--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,14 +418,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -474,22 +474,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consulta de horarios disponibles</t>
+          <t>Mostrar ejemplares disponibles para reserva</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá consultar y mostrar únicamente los horarios disponibles de los médicos.</t>
+          <t>El sistema deberá mostrar únicamente los ejemplares que se encuentren disponibles para reserva.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Consultar horarios disponibles</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -506,17 +506,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visualización de datos del médico</t>
+          <t>Mostrar información del ejemplar antes de confirmar</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar el nombre y la especialidad del médico junto con los horarios disponibles.</t>
+          <t>El sistema deberá mostrar el título, autor, categoría y código del ejemplar antes de confirmar la reserva.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Consultar horarios disponibles</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -538,49 +538,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Actualización de disponibilidad</t>
+          <t>Registrar reserva asociada al estudiante</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad de horarios inmediatamente después de registrar una cita.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Consultar horarios disponibles</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RNF-001</t>
+          <t>RF-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tiempo de respuesta de consulta</t>
+          <t>Cambiar estado del ejemplar a reservado</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá responder a la consulta de horarios disponibles en menos de tres segundos.</t>
+          <t>El sistema deberá cambiar el estado del ejemplar de disponible a reservado inmediatamente después de confirmar la reserva.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Consultar horarios disponibles</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -592,27 +592,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RNF-002</t>
+          <t>RF-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Visualización en tiempo real</t>
+          <t>Impedir reservas sobre ejemplares ya reservados</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar la información de horarios en tiempo real.</t>
+          <t>El sistema deberá impedir que otro estudiante reserve un ejemplar que ya tenga una reserva activa.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Consultar horarios disponibles</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RF-004</t>
+          <t>RF-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Registrar pacientes nuevos</t>
+          <t>Mostrar confirmación de reserva</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar pacientes nuevos.</t>
+          <t>El sistema deberá mostrar una confirmación cuando la reserva se registre correctamente.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar pacientes</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -656,7 +656,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RF-005</t>
+          <t>RF-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -666,29 +666,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Validar documento de identidad</t>
+          <t>Informar fecha límite de recogida</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá validar el documento de identidad del paciente.</t>
+          <t>El sistema deberá informar al estudiante la fecha límite establecida para recoger el ejemplar reservado.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar pacientes</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RF-006</t>
+          <t>RF-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -698,29 +698,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Registrar información obligatoria</t>
+          <t>Actualización inmediata de disponibilidad</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la información obligatoria del paciente.</t>
+          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar pacientes</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RF-007</t>
+          <t>RF-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -730,17 +730,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evitar registros duplicados</t>
+          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá evitar registros duplicados de pacientes.</t>
+          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar pacientes</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RF-008</t>
+          <t>RF-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -762,29 +762,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Editar información del paciente</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir editar posteriormente la información del paciente.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar pacientes</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RF-009</t>
+          <t>RF-011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Consultar agenda médica</t>
+          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá consultar la agenda médica mostrando las citas del día y el nombre del paciente.</t>
+          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 - Consultar agenda médica</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -813,8 +813,296 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RF-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Registrar devolución de libro</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RF-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Verificar préstamo relacionado</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RF-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Actualizar información de préstamo</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RF-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mostrar mensaje de confirmación de devolución</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RF-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Continuar proceso con datos correctos</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RF-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Registrar mascota</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá registrar mascota.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RF-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>El libro debe existir en el sistema</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el libro debe existir en el sistema.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RF-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RF-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -426,7 +426,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impedir reservas sobre ejemplares ya reservados</t>
+          <t>Impedir reserva de ejemplar con reserva activa</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva</t>
+          <t>Mostrar confirmación de reserva registrada</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Actualizar información de préstamo</t>
+          <t>Actualizar información del préstamo</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Registrar Libro</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">

--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mostrar ejemplares disponibles para reserva</t>
+          <t>Consulta de ejemplares disponibles</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mostrar información del ejemplar antes de confirmar</t>
+          <t>Visualización de detalles del ejemplar</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registrar reserva asociada al estudiante</t>
+          <t>Registro de reserva de ejemplar</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cambiar estado del ejemplar a reservado</t>
+          <t>Actualización de estado del ejemplar</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impedir reserva de ejemplar con reserva activa</t>
+          <t>Bloqueo de reserva de ejemplar ya reservado</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva registrada</t>
+          <t>Confirmación de reserva exitosa</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Informar fecha límite de recogida</t>
+          <t>Notificación de fecha límite de recogida</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Actualización inmediata de disponibilidad</t>
+          <t>Inmediatez en la actualización de estado</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
+          <t>El sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá el sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Registrar devolución de libro</t>
+          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
+          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verificar préstamo relacionado</t>
+          <t>Registrar devolución de libro</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
+          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Actualizar información del préstamo</t>
+          <t>Verificar préstamo relacionado</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
+          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de confirmación de devolución</t>
+          <t>Actualizar información de préstamo</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Continuar proceso con datos correctos</t>
+          <t>Mostrar mensaje de confirmación de devolución</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Registrar Libro</t>
+          <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar mascota.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El libro debe existir en el sistema</t>
+          <t>Registrar mascota</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el libro debe existir en el sistema.</t>
+          <t>El sistema deberá registrar mascota.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>El libro debe existir en el sistema</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá el libro debe existir en el sistema.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1082,27 +1082,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RF-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consulta de ejemplares disponibles</t>
+          <t>Mostrar ejemplares disponibles para reserva</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visualización de detalles del ejemplar</t>
+          <t>Mostrar información del ejemplar antes de confirmar</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registro de reserva de ejemplar</t>
+          <t>Registrar reserva del ejemplar</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Actualización de estado del ejemplar</t>
+          <t>Cambiar estado del ejemplar a reservado</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bloqueo de reserva de ejemplar ya reservado</t>
+          <t>Impedir reservas duplicadas activas</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Confirmación de reserva exitosa</t>
+          <t>Mostrar confirmación de reserva</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Notificación de fecha límite de recogida</t>
+          <t>Informar fecha límite de recogida</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inmediatez en la actualización de estado</t>
+          <t>Actualización inmediata de disponibilidad</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
+          <t>El sistema deberá actualizar la disponibilidad del ejemplar inmediatamente después de confirmar una reserva.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
+          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
+          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
+          <t>Registrar devolución de libro</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Registrar devolución de libro</t>
+          <t>Verificar préstamo relacionado</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
+          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verificar préstamo relacionado</t>
+          <t>Actualizar información del préstamo</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Actualizar información de préstamo</t>
+          <t>Mostrar mensaje de confirmación de devolución</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de confirmación de devolución</t>
+          <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos de la devolución sean correctos.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Continuar proceso con datos correctos</t>
+          <t>Registrar mascota</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá registrar mascota.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>El libro debe existir en el sistema</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar mascota.</t>
+          <t>El sistema deberá el libro debe existir en el sistema.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El libro debe existir en el sistema</t>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el libro debe existir en el sistema.</t>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1101,40 +1101,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RF-021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mostrar ejemplares disponibles para reserva</t>
+          <t>Consulta de ejemplares disponibles</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mostrar información del ejemplar antes de confirmar</t>
+          <t>Visualización de detalles del ejemplar</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registrar reserva del ejemplar</t>
+          <t>Registro de reserva</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cambiar estado del ejemplar a reservado</t>
+          <t>Actualización de estado del ejemplar</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impedir reservas duplicadas activas</t>
+          <t>Bloqueo de reserva duplicada</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva</t>
+          <t>Confirmación de reserva</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Informar fecha límite de recogida</t>
+          <t>Información de fecha límite de recogida</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Actualización inmediata de disponibilidad</t>
+          <t>Inmediatez en la actualización de disponibilidad</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad del ejemplar inmediatamente después de confirmar una reserva.</t>
+          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
+          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
+          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>El sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá el sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Continuar proceso con datos correctos</t>
+          <t>Permitir continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos de la devolución sean correctos.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -1101,8 +1101,264 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RF-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Consultar historial de préstamos del estudiante</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado que realiza la consulta.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RF-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ordenar historial de préstamos por fecha</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RF-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mostrar detalles del préstamo en el historial</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RF-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Filtrar préstamos por estado</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir filtrar los préstamos del historial por estado.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RF-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mostrar mensaje de historial vacío</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RF-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Impedir consulta de historial ajeno</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RF-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RF-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>No se permite la modificación de los registros desde esta consulta</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá no se permite la modificación de los registros desde esta consulta.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Registrar libro</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">

--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consulta de ejemplares disponibles</t>
+          <t>Mostrar ejemplares disponibles para reserva</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visualización de detalles del ejemplar</t>
+          <t>Mostrar detalles del ejemplar antes de confirmar reserva</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registro de reserva</t>
+          <t>Registrar reserva asociada al estudiante autenticado</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Actualización de estado del ejemplar</t>
+          <t>Cambiar estado del ejemplar a reservado</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bloqueo de reserva duplicada</t>
+          <t>Impedir reserva de ejemplar con reserva activa</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Confirmación de reserva</t>
+          <t>Mostrar confirmación de reserva registrada</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Información de fecha límite de recogida</t>
+          <t>Informar fecha límite para recoger ejemplar</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inmediatez en la actualización de disponibilidad</t>
+          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
+          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>La disponibilidad debe actualizarse inmediatamente después de confirmar una reserva</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá la disponibilidad debe actualizarse inmediatamente después de que el estudiante confirme una reserva.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Registrar devolución de libro</t>
+          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
+          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verificar préstamo relacionado</t>
+          <t>Registrar devolución de libro</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
+          <t>El sistema deberá permitir registrar la devolución de un libro.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Actualizar información del préstamo</t>
+          <t>Verificar existencia de préstamo</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
+          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de confirmación de devolución</t>
+          <t>Actualizar información del préstamo</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Permitir continuar proceso con datos correctos</t>
+          <t>Mostrar mensaje de devolución registrada</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Registrar libro</t>
+          <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar mascota.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El libro debe existir en el sistema</t>
+          <t>Registrar mascota</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el libro debe existir en el sistema.</t>
+          <t>El sistema deberá registrar mascota.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>El libro debe existir en el sistema</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá el libro debe existir en el sistema.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Consultar historial de préstamos del estudiante</t>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado que realiza la consulta.</t>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ordenar historial de préstamos por fecha</t>
+          <t>Consultar historial de préstamos</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
+          <t>El sistema deberá consultar el historial de los préstamos que el estudiante autenticado ha realizado en la biblioteca.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mostrar detalles del préstamo en el historial</t>
+          <t>Mostrar préstamos del estudiante autenticado</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual.</t>
+          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Filtrar préstamos por estado</t>
+          <t>Ordenar préstamos por fecha descendente</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir filtrar los préstamos del historial por estado.</t>
+          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de historial vacío</t>
+          <t>Mostrar detalles de cada préstamo</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
+          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual (activo, devuelto, vencido).</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Impedir consulta de historial ajeno</t>
+          <t>Filtrar préstamos por estado</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+          <t>El sistema deberá permitir filtrar los préstamos por estado.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+          <t>Mostrar mensaje sin préstamos</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1338,27 +1338,91 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Impedir que un estudiante consulte el historial de otro estudiante</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RF-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RF-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>No se permite la modificación de los registros desde esta consulta</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>El sistema deberá no se permite la modificación de los registros desde esta consulta.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 Consultar historial</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,15 +418,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,17 +474,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mostrar ejemplares disponibles para reserva</t>
+          <t>Registrar ejemplar físico asociado a libro y sucursal</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar únicamente los ejemplares que se encuentren disponibles para reserva.</t>
+          <t>El sistema deberá permitir registrar un ejemplar asociándolo a un libro y sucursal existentes, asignando automáticamente el estado inicial "disponible" y registrando su condición física.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mostrar detalles del ejemplar antes de confirmar reserva</t>
+          <t>Generar automáticamente código de identificación del ejemplar</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar el título, autor, categoría y código del ejemplar antes de confirmar la reserva.</t>
+          <t>El sistema deberá generar automáticamente el código de identificación del ejemplar con el formato bib-{sucursal}-{categoría}-{secuencial}.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registrar reserva asociada al estudiante autenticado</t>
+          <t>Dar de baja un ejemplar registrando el motivo</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado.</t>
+          <t>El sistema deberá permitir dar de baja un ejemplar registrando el motivo correspondiente.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cambiar estado del ejemplar a reservado</t>
+          <t>Impedir dar de baja un ejemplar prestado o dado de baja</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá cambiar el estado del ejemplar de disponible a reservado inmediatamente después de confirmar la reserva.</t>
+          <t>El sistema deberá impedir dar de baja un ejemplar que se encuentre actualmente prestado o ya dado de baja.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impedir reserva de ejemplar con reserva activa</t>
+          <t>Consultar ejemplares asociados a un libro específico</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá impedir que otro estudiante reserve un ejemplar que ya tenga una reserva activa.</t>
+          <t>El sistema deberá permitir consultar los ejemplares asociados a un libro específico con su estado actual.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva registrada</t>
+          <t>El libro y la sucursal deben existir previamente en el sistema</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar una confirmación cuando la reserva se registre correctamente.</t>
+          <t>El sistema deberá el libro y la sucursal deben existir previamente en el sistema.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Informar fecha límite para recoger ejemplar</t>
+          <t>El código de ejemplar debe ser único en todo el sistema</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá informar al estudiante la fecha límite establecida para recoger el ejemplar reservado.</t>
+          <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
+          <t>El secuencial del código se genera automáticamente por sucursal y categoría</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
+          <t>El sistema deberá el secuencial del código se genera automáticamente por sucursal y categoría.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -730,17 +730,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
+          <t>Registrar préstamo de ejemplar disponible</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
+          <t>El sistema deberá permitir registrar un préstamo seleccionando un ejemplar disponible y un lector.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>La disponibilidad debe actualizarse inmediatamente después de confirmar una reserva</t>
+          <t>Verificar estado disponible del ejemplar</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la disponibilidad debe actualizarse inmediatamente después de que el estudiante confirme una reserva.</t>
+          <t>El sistema deberá verificar que el ejemplar se encuentre en estado disponible antes de registrar el préstamo.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>Verificar que el lector esté activo</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá verificar que el lector esté activo en el sistema.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -816,39 +816,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RF-012</t>
+          <t>RNF-001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
+          <t>Verificar límite máximo de préstamos activos</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RF-013</t>
+          <t>RF-012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -858,17 +858,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Registrar devolución de libro</t>
+          <t>Impedir préstamo con préstamos vencidos</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar la devolución de un libro.</t>
+          <t>El sistema deberá impedir el préstamo cuando el lector tenga préstamos vencidos sin devolver.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RF-014</t>
+          <t>RF-013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,29 +890,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verificar existencia de préstamo</t>
+          <t>Calcular fecha de devolución esperada</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro.</t>
+          <t>El sistema deberá calcular automáticamente la fecha de devolución esperada según los días configurados.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RF-015</t>
+          <t>RF-014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Actualizar información del préstamo</t>
+          <t>Cambiar estado del ejemplar a prestado</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+          <t>El sistema deberá cambiar el estado del ejemplar a "prestado" inmediatamente después de registrar el préstamo.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RF-016</t>
+          <t>RF-015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de devolución registrada</t>
+          <t>Registrar bibliotecario operador</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+          <t>El sistema deberá registrar el bibliotecario que realizó la operación.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -976,7 +976,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RF-017</t>
+          <t>RF-016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Continuar proceso con datos correctos</t>
+          <t>Solo los bibliotecarios y administradores pueden registrar préstamos</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá solo los bibliotecarios y administradores pueden registrar préstamos.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,7 +1008,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RF-018</t>
+          <t>RF-017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Un lector puede tener como máximo 3 préstamos activos simultáneamente</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar mascota.</t>
+          <t>El sistema deberá un lector puede tener como máximo 3 préstamos activos simultáneamente.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1040,27 +1040,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RF-019</t>
+          <t>RNF-002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El libro debe existir en el sistema</t>
+          <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el libro debe existir en el sistema.</t>
+          <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RF-020</t>
+          <t>RF-018</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>No se permiten préstamos a lectores con devoluciones pendientes vencidas</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá no se permiten préstamos a lectores con devoluciones pendientes vencidas.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RF-021</t>
+          <t>RF-019</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+          <t>El identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+          <t>El sistema deberá el identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RF-022</t>
+          <t>RF-020</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consultar historial de préstamos</t>
+          <t>Buscar libros por término, categoría o sucursal</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá consultar el historial de los préstamos que el estudiante autenticado ha realizado en la biblioteca.</t>
+          <t>El sistema deberá permitir buscar libros por título, autor o isbn utilizando un término de búsqueda.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,7 +1168,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RF-023</t>
+          <t>RF-021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mostrar préstamos del estudiante autenticado</t>
+          <t>Filtrar resultados por categoría y sucursal</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado.</t>
+          <t>El sistema deberá permitir filtrar los resultados por categoría del libro y por sucursal con ejemplares disponibles.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1200,7 +1200,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RF-024</t>
+          <t>RF-022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ordenar préstamos por fecha descendente</t>
+          <t>Mostrar cantidad de ejemplares disponibles</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
+          <t>El sistema deberá mostrar la cantidad de ejemplares disponibles de cada libro en los resultados de búsqueda.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RF-025</t>
+          <t>RF-023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1242,29 +1242,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mostrar detalles de cada préstamo</t>
+          <t>Paginar resultados de búsqueda</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual (activo, devuelto, vencido).</t>
+          <t>El sistema deberá paginar los resultados de búsqueda cuando excedan 20 registros.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RF-026</t>
+          <t>RF-024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Filtrar préstamos por estado</t>
+          <t>Consultar disponibilidad detallada por sucursal</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir filtrar los préstamos por estado.</t>
+          <t>El sistema deberá permitir consultar la disponibilidad detallada de un libro mostrando por cada sucursal el total de ejemplares y la cantidad disponible.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RF-027</t>
+          <t>RF-025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1306,49 +1306,49 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mostrar mensaje sin préstamos</t>
+          <t>Los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
+          <t>El sistema deberá los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RF-028</t>
+          <t>RNF-003</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Impedir que un estudiante consulte el historial de otro estudiante</t>
+          <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+          <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RF-029</t>
+          <t>RF-026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1370,17 +1370,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+          <t>La búsqueda utiliza coincidencia parcial para permitir resultados aproximados</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+          <t>El sistema deberá la búsqueda utiliza coincidencia parcial para permitir resultados aproximados.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,37 +1392,741 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>RNF-004</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la búsqueda utiliza coincidencia parcial (ilike) para permitir resultados aproximados. La disponibilidad se calcula en tiempo real consultando el estado actual de los ejemplares.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RF-027</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Registrar la devolución de un ejemplar</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar la devolución de un ejemplar prestado.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RF-028</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Verificar existencia de préstamo activo</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que exista un préstamo activo relacionado con el ejemplar.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RF-029</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Actualizar información del préstamo después de la devolución</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>RF-030</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No se permite la modificación de los registros desde esta consulta</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>El sistema deberá no se permite la modificación de los registros desde esta consulta.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mostrar mensaje de confirmación de devolución</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RF-031</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RF-032</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RF-033</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RF-034</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Solicitar transferencia de ejemplar disponible</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RF-035</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Verificar disponibilidad del ejemplar</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RF-036</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Registrar sucursal de origen y destino</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RF-037</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RF-038</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>El ejemplar debe estar disponible</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el ejemplar debe estar disponible.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RF-039</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Las sucursales de origen y destino deben ser diferentes</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RF-040</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RF-041</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Registrar un libro con metadatos bibliográficos</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RF-042</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Validar unicidad y formato de isbn</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>RF-043</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Modificar la información bibliográfica de un libro existente</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RF-044</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Consultar libros aplicando filtros por título, autor y categoría</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>RF-045</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RF-046</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RF-047</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RF-048</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>El libro debe estar registrado antes de poder crear ejemplares físicos asociados</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el libro debe estar registrado antes de poder crear ejemplares físicos asociados.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de entrada" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Registrar ejemplar físico asociado a libro y sucursal</t>
+          <t>Registrar ejemplar asociado a libro y sucursal</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Generar automáticamente código de identificación del ejemplar</t>
+          <t>Generar código de identificación automático</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Registrar préstamo de ejemplar disponible</t>
+          <t>Registrar préstamo de ejemplar a lector</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verificar límite máximo de préstamos activos</t>
+          <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Impedir préstamo con préstamos vencidos</t>
+          <t>Impedir préstamo cuando el lector tenga préstamos vencidos</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cambiar estado del ejemplar a prestado</t>
+          <t>Cambiar estado del ejemplar a 'prestado'</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Registrar bibliotecario operador</t>
+          <t>Registrar bibliotecario que realizó la operación</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Registrar la devolución de un ejemplar</t>
+          <t>Registrar la devolución de un ejemplar prestado</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de confirmación de devolución</t>
+          <t>Mostrar mensaje de devolución registrada</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+          <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>El ejemplar debe existir en el sistema</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá el ejemplar debe existir en el sistema.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1658,22 +1658,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Solicitar transferencia de ejemplar disponible</t>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verificar disponibilidad del ejemplar</t>
+          <t>Solicitar transferencia de ejemplar disponible</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
+          <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Registrar sucursal de origen y destino</t>
+          <t>Verificar disponibilidad del ejemplar</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
+          <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+          <t>Registrar sucursal de origen y destino</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>El ejemplar debe estar disponible</t>
+          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el ejemplar debe estar disponible.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las sucursales de origen y destino deben ser diferentes</t>
+          <t>El ejemplar debe estar disponible</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
+          <t>El sistema deberá el ejemplar debe estar disponible.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
+          <t>Las sucursales de origen y destino deben ser diferentes</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
+          <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Registrar un libro con metadatos bibliográficos</t>
+          <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
+          <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Gestión de libros</t>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Validar unicidad y formato de isbn</t>
+          <t>Registrar un libro con datos bibliográficos</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
+          <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Modificar la información bibliográfica de un libro existente</t>
+          <t>Validar formato y unicidad de isbn</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
+          <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Consultar libros aplicando filtros por título, autor y categoría</t>
+          <t>Modificar la información bibliográfica de un libro existente</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
+          <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
+          <t>Consultar libros aplicando filtros por título, autor y categoría</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
+          <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
+          <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
+          <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pendiente de definición y validación</t>
+          <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
+          <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
+          <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pendiente de validación</t>
+          <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
@@ -2106,27 +2106,91 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RF-049</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No se permite registrar dos libros con el mismo ISBN</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá no se permite registrar dos libros con el mismo ISBN.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RF-050</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>El libro debe estar registrado antes de poder crear ejemplares físicos asociados</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>El sistema deberá el libro debe estar registrado antes de poder crear ejemplares físicos asociados.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Pendiente de validación</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F53"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_diseno.xlsx
+++ b/output/xlsx/matriz_entrada_diseno.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de entrada'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Matriz de entrada'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +28,42 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF212529"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F8FC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,14 +71,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFC8D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFC8D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFC8D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFC8D6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,1775 +465,1776 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Historia de origen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Estado de revisión</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>RF-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Registrar ejemplar asociado a libro y sucursal</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar un ejemplar asociándolo a un libro y sucursal existentes, asignando automáticamente el estado inicial "disponible" y registrando su condición física.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="44.5" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>RF-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Generar código de identificación automático</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá generar automáticamente el código de identificación del ejemplar con el formato bib-{sucursal}-{categoría}-{secuencial}.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>RF-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Dar de baja un ejemplar registrando el motivo</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir dar de baja un ejemplar registrando el motivo correspondiente.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>RF-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Impedir dar de baja un ejemplar prestado o dado de baja</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá impedir dar de baja un ejemplar que se encuentre actualmente prestado o ya dado de baja.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>RF-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Consultar ejemplares asociados a un libro específico</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir consultar los ejemplares asociados a un libro específico con su estado actual.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>RF-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>El libro y la sucursal deben existir previamente en el sistema</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el libro y la sucursal deben existir previamente en el sistema.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RF-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>El código de ejemplar debe ser único en todo el sistema</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>RF-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>El secuencial del código se genera automáticamente por sucursal y categoría</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el secuencial del código se genera automáticamente por sucursal y categoría.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RF-009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Registrar préstamo de ejemplar a lector</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar un préstamo seleccionando un ejemplar disponible y un lector.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>RF-010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Verificar estado disponible del ejemplar</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el ejemplar se encuentre en estado disponible antes de registrar el préstamo.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RF-011</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Verificar que el lector esté activo</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el lector esté activo en el sistema.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="44.5" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>RNF-001</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>RF-012</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Impedir préstamo cuando el lector tenga préstamos vencidos</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá impedir el préstamo cuando el lector tenga préstamos vencidos sin devolver.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>RF-013</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Calcular fecha de devolución esperada</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá calcular automáticamente la fecha de devolución esperada según los días configurados.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>RF-014</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Cambiar estado del ejemplar a 'prestado'</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá cambiar el estado del ejemplar a "prestado" inmediatamente después de registrar el préstamo.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="31" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>RF-015</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Registrar bibliotecario que realizó la operación</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá registrar el bibliotecario que realizó la operación.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="31" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>RF-016</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Solo los bibliotecarios y administradores pueden registrar préstamos</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá solo los bibliotecarios y administradores pueden registrar préstamos.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>RF-017</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Un lector puede tener como máximo 3 préstamos activos simultáneamente</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá un lector puede tener como máximo 3 préstamos activos simultáneamente.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>RNF-002</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="31" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>RF-018</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>No se permiten préstamos a lectores con devoluciones pendientes vencidas</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá no se permiten préstamos a lectores con devoluciones pendientes vencidas.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="98.5" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>RF-019</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>El identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>RF-020</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Buscar libros por término, categoría o sucursal</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir buscar libros por título, autor o isbn utilizando un término de búsqueda.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44.5" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>RF-021</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Filtrar resultados por categoría y sucursal</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir filtrar los resultados por categoría del libro y por sucursal con ejemplares disponibles.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44.5" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>RF-022</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Mostrar cantidad de ejemplares disponibles</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá mostrar la cantidad de ejemplares disponibles de cada libro en los resultados de búsqueda.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="31" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>RF-023</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Paginar resultados de búsqueda</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá paginar los resultados de búsqueda cuando excedan 20 registros.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>RF-024</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Consultar disponibilidad detallada por sucursal</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir consultar la disponibilidad detallada de un libro mostrando por cada sucursal el total de ejemplares y la cantidad disponible.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44.5" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>RF-025</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44.5" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>RNF-003</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="31" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>RF-026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>La búsqueda utiliza coincidencia parcial para permitir resultados aproximados</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá la búsqueda utiliza coincidencia parcial para permitir resultados aproximados.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>RNF-004</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la búsqueda utiliza coincidencia parcial (ilike) para permitir resultados aproximados. La disponibilidad se calcula en tiempo real consultando el estado actual de los ejemplares.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="31" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>RF-027</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Registrar la devolución de un ejemplar prestado</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar la devolución de un ejemplar prestado.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="31" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>RF-028</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Verificar existencia de préstamo activo</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que exista un préstamo activo relacionado con el ejemplar.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>RF-029</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Actualizar información del préstamo después de la devolución</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>RF-030</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Mostrar mensaje de devolución registrada</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>RF-031</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" ht="31" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>RF-032</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>El ejemplar debe existir en el sistema</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el ejemplar debe existir en el sistema.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>RF-033</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>La devolución debe corresponder a un préstamo registrado</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="71.5" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>RF-034</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="31" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>RF-035</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Solicitar transferencia de ejemplar disponible</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>RF-036</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Verificar disponibilidad del ejemplar</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>RF-037</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Registrar sucursal de origen y destino</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>RF-038</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>RF-039</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>El ejemplar debe estar disponible</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el ejemplar debe estar disponible.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>RF-040</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Las sucursales de origen y destino deben ser diferentes</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="71.5" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>RF-041</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44.5" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>RF-042</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Registrar un libro con datos bibliográficos</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Registrar un libro con datos bibliográficos correctos</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44.5" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>RF-043</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Validar formato y unicidad de isbn</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>RF-044</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Modificar la información bibliográfica de un libro existente</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>RF-045</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Consultar libros aplicando filtros por título, autor y categoría</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>RF-046</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>RF-047</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>Pendiente de definición y validación</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>RF-048</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="31" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>RF-049</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>No se permite registrar dos libros con el mismo ISBN</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá no se permite registrar dos libros con el mismo ISBN.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Pendiente de validación</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="31" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>RF-050</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>El libro debe estar registrado antes de poder crear ejemplares físicos asociados</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el libro debe estar registrado antes de poder crear ejemplares físicos asociados.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Pendiente de validación</t>
         </is>
@@ -2192,5 +2243,6 @@
   </sheetData>
   <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>